--- a/Excel/SkillSuitConfig.xlsx
+++ b/Excel/SkillSuitConfig.xlsx
@@ -1803,7 +1803,7 @@
         <v>1</v>
       </c>
       <c r="K6" s="2">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L6" s="1">
         <v>0</v>
@@ -1871,7 +1871,7 @@
         <v>1</v>
       </c>
       <c r="K7" s="2">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L7" s="1">
         <v>0</v>
@@ -1942,7 +1942,7 @@
         <v>1</v>
       </c>
       <c r="K8" s="2">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L8" s="1">
         <v>0</v>
@@ -2013,7 +2013,7 @@
         <v>1</v>
       </c>
       <c r="K9" s="2">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L9" s="1">
         <v>0</v>
@@ -2084,7 +2084,7 @@
         <v>1</v>
       </c>
       <c r="K10" s="2">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L10" s="1">
         <v>0</v>
@@ -2155,7 +2155,7 @@
         <v>1</v>
       </c>
       <c r="K11" s="2">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L11" s="1">
         <v>0</v>
@@ -2226,7 +2226,7 @@
         <v>1</v>
       </c>
       <c r="K12" s="2">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L12" s="1">
         <v>0</v>
@@ -2317,7 +2317,7 @@
         <v>4</v>
       </c>
       <c r="K15" s="2">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L15" s="1">
         <v>0</v>
@@ -2385,7 +2385,7 @@
         <v>4</v>
       </c>
       <c r="K16" s="2">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L16" s="1">
         <v>0</v>
@@ -2453,7 +2453,7 @@
         <v>1</v>
       </c>
       <c r="K17" s="2">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L17" s="1">
         <v>0</v>
@@ -2524,7 +2524,7 @@
         <v>4</v>
       </c>
       <c r="K18" s="2">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L18" s="1">
         <v>0</v>
@@ -2592,7 +2592,7 @@
         <v>4</v>
       </c>
       <c r="K19" s="2">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L19" s="1">
         <v>0</v>
@@ -2671,7 +2671,7 @@
         <v>4</v>
       </c>
       <c r="K21" s="2">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L21" s="1">
         <v>0</v>
@@ -2743,7 +2743,7 @@
         <v>4</v>
       </c>
       <c r="K22" s="2">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L22" s="1">
         <v>0</v>
@@ -2815,7 +2815,7 @@
         <v>4</v>
       </c>
       <c r="K23" s="2">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L23" s="1">
         <v>0</v>
@@ -2887,7 +2887,7 @@
         <v>4</v>
       </c>
       <c r="K24" s="2">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L24" s="1">
         <v>0</v>
@@ -2987,7 +2987,7 @@
         <v>5</v>
       </c>
       <c r="K26" s="2">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L26" s="1">
         <v>0</v>
@@ -3059,7 +3059,7 @@
         <v>5</v>
       </c>
       <c r="K27" s="2">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L27" s="1">
         <v>0</v>
@@ -3131,7 +3131,7 @@
         <v>5</v>
       </c>
       <c r="K28" s="2">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L28" s="1">
         <v>0</v>
@@ -3203,7 +3203,7 @@
         <v>5</v>
       </c>
       <c r="K29" s="2">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L29" s="1">
         <v>0</v>
@@ -3282,7 +3282,7 @@
         <v>1</v>
       </c>
       <c r="K33" s="2">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L33" s="1">
         <v>0</v>
@@ -3350,7 +3350,7 @@
         <v>1</v>
       </c>
       <c r="K34" s="2">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L34" s="1">
         <v>0</v>
@@ -3421,7 +3421,7 @@
         <v>1</v>
       </c>
       <c r="K35" s="2">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L35" s="1">
         <v>0</v>
@@ -3492,7 +3492,7 @@
         <v>1</v>
       </c>
       <c r="K36" s="2">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L36" s="1">
         <v>0</v>
@@ -3563,7 +3563,7 @@
         <v>1</v>
       </c>
       <c r="K37" s="2">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L37" s="1">
         <v>0</v>
@@ -3634,7 +3634,7 @@
         <v>1</v>
       </c>
       <c r="K38" s="2">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L38" s="1">
         <v>0</v>
@@ -3705,7 +3705,7 @@
         <v>1</v>
       </c>
       <c r="K39" s="2">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L39" s="1">
         <v>0</v>
@@ -3783,7 +3783,7 @@
         <v>4</v>
       </c>
       <c r="K41" s="2">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L41" s="1">
         <v>0</v>
@@ -3851,7 +3851,7 @@
         <v>4</v>
       </c>
       <c r="K42" s="2">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L42" s="1">
         <v>0</v>
@@ -3919,7 +3919,7 @@
         <v>1</v>
       </c>
       <c r="K43" s="2">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L43" s="1">
         <v>0</v>
@@ -3990,7 +3990,7 @@
         <v>4</v>
       </c>
       <c r="K44" s="2">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L44" s="1">
         <v>0</v>
@@ -4058,7 +4058,7 @@
         <v>4</v>
       </c>
       <c r="K45" s="2">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L45" s="1">
         <v>0</v>
@@ -4105,7 +4105,9 @@
       <c r="F46" s="2"/>
       <c r="I46" s="2"/>
       <c r="J46" s="2"/>
-      <c r="K46" s="2"/>
+      <c r="K46" s="2">
+        <v>9</v>
+      </c>
       <c r="S46" s="2"/>
       <c r="T46" s="2"/>
       <c r="U46" s="2"/>
@@ -4136,9 +4138,7 @@
       <c r="J47" s="2">
         <v>4</v>
       </c>
-      <c r="K47" s="2">
-        <v>5</v>
-      </c>
+      <c r="K47" s="2"/>
       <c r="L47" s="1">
         <v>0</v>
       </c>
@@ -4209,7 +4209,7 @@
         <v>4</v>
       </c>
       <c r="K48" s="2">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L48" s="1">
         <v>0</v>
@@ -4281,7 +4281,7 @@
         <v>4</v>
       </c>
       <c r="K49" s="2">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L49" s="1">
         <v>0</v>
@@ -4353,7 +4353,7 @@
         <v>4</v>
       </c>
       <c r="K50" s="2">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L50" s="1">
         <v>0</v>
@@ -4451,7 +4451,7 @@
         <v>5</v>
       </c>
       <c r="K52" s="2">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L52" s="1">
         <v>0</v>
@@ -4523,7 +4523,7 @@
         <v>5</v>
       </c>
       <c r="K53" s="2">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L53" s="1">
         <v>0</v>
@@ -4595,7 +4595,7 @@
         <v>5</v>
       </c>
       <c r="K54" s="2">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L54" s="1">
         <v>0</v>
@@ -4667,7 +4667,7 @@
         <v>5</v>
       </c>
       <c r="K55" s="2">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L55" s="1">
         <v>0</v>
@@ -4712,7 +4712,6 @@
     <row r="56" customHeight="1" spans="3:29">
       <c r="I56" s="2"/>
       <c r="J56" s="2"/>
-      <c r="K56" s="2"/>
     </row>
     <row r="57" s="3" customFormat="1" customHeight="1"/>
     <row r="58" customHeight="1" spans="3:29">
@@ -4746,7 +4745,7 @@
         <v>1</v>
       </c>
       <c r="K59" s="2">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L59" s="1">
         <v>0</v>
@@ -4814,7 +4813,7 @@
         <v>1</v>
       </c>
       <c r="K60" s="2">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L60" s="1">
         <v>0</v>
@@ -4885,7 +4884,7 @@
         <v>1</v>
       </c>
       <c r="K61" s="2">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L61" s="1">
         <v>0</v>
@@ -4956,7 +4955,7 @@
         <v>1</v>
       </c>
       <c r="K62" s="2">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L62" s="1">
         <v>0</v>
@@ -5027,7 +5026,7 @@
         <v>1</v>
       </c>
       <c r="K63" s="2">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L63" s="1">
         <v>0</v>
@@ -5098,7 +5097,7 @@
         <v>1</v>
       </c>
       <c r="K64" s="2">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L64" s="1">
         <v>0</v>
@@ -5169,7 +5168,7 @@
         <v>1</v>
       </c>
       <c r="K65" s="2">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L65" s="1">
         <v>0</v>
@@ -5247,7 +5246,7 @@
         <v>4</v>
       </c>
       <c r="K67" s="2">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L67" s="1">
         <v>0</v>
@@ -5315,7 +5314,7 @@
         <v>4</v>
       </c>
       <c r="K68" s="2">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L68" s="1">
         <v>0</v>
@@ -5383,7 +5382,7 @@
         <v>1</v>
       </c>
       <c r="K69" s="2">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L69" s="1">
         <v>0</v>
@@ -5454,7 +5453,7 @@
         <v>4</v>
       </c>
       <c r="K70" s="2">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L70" s="1">
         <v>0</v>
@@ -5522,7 +5521,7 @@
         <v>4</v>
       </c>
       <c r="K71" s="2">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L71" s="1">
         <v>0</v>
@@ -5601,7 +5600,7 @@
         <v>4</v>
       </c>
       <c r="K73" s="2">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L73" s="1">
         <v>0</v>
@@ -5673,7 +5672,7 @@
         <v>4</v>
       </c>
       <c r="K74" s="2">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L74" s="1">
         <v>0</v>
@@ -5745,7 +5744,7 @@
         <v>4</v>
       </c>
       <c r="K75" s="2">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L75" s="1">
         <v>0</v>
@@ -5817,7 +5816,7 @@
         <v>4</v>
       </c>
       <c r="K76" s="2">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L76" s="1">
         <v>0</v>
@@ -5915,7 +5914,7 @@
         <v>5</v>
       </c>
       <c r="K78" s="2">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L78" s="1">
         <v>0</v>
@@ -5987,7 +5986,7 @@
         <v>5</v>
       </c>
       <c r="K79" s="2">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L79" s="1">
         <v>0</v>
@@ -6059,7 +6058,7 @@
         <v>5</v>
       </c>
       <c r="K80" s="2">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L80" s="1">
         <v>0</v>
@@ -6131,7 +6130,7 @@
         <v>5</v>
       </c>
       <c r="K81" s="2">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L81" s="1">
         <v>0</v>
